--- a/0. Rundown RKT.xlsx
+++ b/0. Rundown RKT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\persiapan-rkt-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC6071C-444B-43F4-953F-B641E13967E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F4FEDC-AD53-4678-9209-70CB7BE13ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,7 +205,6 @@
   </si>
   <si>
     <t>Evaluasi tahun sebelumnya (aspirasi dari seluruh Ustadz/ah):
-- Kesantrian
 - Tahfidz (berapa banyak juziyah dan syahadah santri)
 - Tahsin (berapa banyak yang belum lancar tahsinnya dalam waktu setahun)
 - Aspirasi</t>
@@ -271,10 +270,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,40 +562,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
@@ -723,7 +722,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="120">
+    <row r="18" spans="1:5" ht="105">
       <c r="A18" s="2" t="s">
         <v>35</v>
       </c>
@@ -788,57 +787,57 @@
       <c r="D22" s="2"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0. Rundown RKT.xlsx
+++ b/0. Rundown RKT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\persiapan-rkt-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MABAIZ\Persiapan RKT 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F4FEDC-AD53-4678-9209-70CB7BE13ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2F776C-950D-4564-A28A-215ABE671106}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19455" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,12 +20,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>RAPAT KERJA TAHUNAN (RKT) GABUNGAN</t>
   </si>
@@ -208,6 +203,12 @@
 - Tahfidz (berapa banyak juziyah dan syahadah santri)
 - Tahsin (berapa banyak yang belum lancar tahsinnya dalam waktu setahun)
 - Aspirasi</t>
+  </si>
+  <si>
+    <t>Tilawah Al-Quran</t>
+  </si>
+  <si>
+    <t>Ust. Ahmad Yudha Nugraha, S.Pd.</t>
   </si>
 </sst>
 </file>
@@ -270,10 +271,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
@@ -562,40 +563,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
@@ -624,220 +625,230 @@
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="30">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="30">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="30">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="30">
       <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="30">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" ht="30">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="30">
+      <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" ht="30">
-      <c r="A17" s="2" t="s">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="30">
+      <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="1" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="105">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:5" ht="105">
+      <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="45">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:5" ht="45">
+      <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" ht="135">
-      <c r="A21" s="2" t="s">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="135">
+      <c r="A22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2" t="s">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0. Rundown RKT.xlsx
+++ b/0. Rundown RKT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MABAIZ\Persiapan RKT 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2F776C-950D-4564-A28A-215ABE671106}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B765D99A-AF58-4819-9026-CF442339ED4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19455" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>RAPAT KERJA TAHUNAN (RKT) GABUNGAN</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Pembukaan</t>
   </si>
   <si>
-    <t>Sekretaris</t>
-  </si>
-  <si>
     <t>08.10 - 09.00</t>
   </si>
   <si>
@@ -136,13 +133,6 @@
   </si>
   <si>
     <t>14.00 - 15.00</t>
-  </si>
-  <si>
-    <t>Kuttab : Ustadzah Mia
-Madrasah : Ustadz Zen</t>
-  </si>
-  <si>
-    <t>Data dari Google Forms (harus) deadline penyampaian aspirasi : Sabtu, 27 Juni 2026</t>
   </si>
   <si>
     <t>15.00 - 16.00</t>
@@ -181,9 +171,6 @@
     <t>16.45 - 17.00</t>
   </si>
   <si>
-    <t>Penutup</t>
-  </si>
-  <si>
     <t>Catatan:</t>
   </si>
   <si>
@@ -208,7 +195,13 @@
     <t>Tilawah Al-Quran</t>
   </si>
   <si>
-    <t>Ust. Ahmad Yudha Nugraha, S.Pd.</t>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Ust. Akhmad Yudha Nugraha, S.Pd.</t>
+  </si>
+  <si>
+    <t>Doa &amp; Penutup</t>
   </si>
 </sst>
 </file>
@@ -271,10 +264,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -554,8 +547,8 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="1" style="1" customWidth="1"/>
@@ -563,40 +556,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
@@ -620,235 +613,230 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="30">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="30">
       <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="30">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="30">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="30">
       <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="60">
+      <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="105">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="45">
       <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="135">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0. Rundown RKT.xlsx
+++ b/0. Rundown RKT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MABAIZ\Persiapan RKT 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B765D99A-AF58-4819-9026-CF442339ED4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9EAEC9-416A-41E2-8A17-0F6A0F7D942D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,22 +186,50 @@
     <t>• Jadwal dapat disesuaikan dengan kebutuhan pelaksanaan.</t>
   </si>
   <si>
+    <t>Tilawah Al-Quran</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Ust. Akhmad Yudha Nugraha, S.Pd.</t>
+  </si>
+  <si>
+    <t>Doa &amp; Penutup</t>
+  </si>
+  <si>
     <t>Evaluasi tahun sebelumnya (aspirasi dari seluruh Ustadz/ah):
 - Tahfidz (berapa banyak juziyah dan syahadah santri)
 - Tahsin (berapa banyak yang belum lancar tahsinnya dalam waktu setahun)
+* Kelas 1 : Ghaisan dan Erina
+* Kelas 2 : Uzzam (parah secara praktek) dan Faiz (URGENT karena sudah kelas 3 sekarang)
+_ Ketika diujikan, sudah siap untuk menghafal. Tapi dalam perjalanannya, ternyata kurang bagus tahsinnya
+_ Kalau bisa, diadakan Bengkel Tahsin Private dengan biaya karena harus fokus dengan anak tertentu (bukan klasikal)
+_ Perlu forum kecil khusus untuk membahas tahsin khusus ini
+_ Mungkin karena musyrif/ah-nya belum fokus private ini
+_ Misalnya, private tahsin di luar jam tahfidznya sehingga harus ada biaya untuk mengajar private-nya
+Ustadz Wahidi
+- Kalau dari orang tua kan taunya SPP yang ada sudah cukup membuat anak jadi lebih baik (beda dengan sekolah yang nggak full 24 jam), kecuali kalau ada kesadaran dari orang tua untuk nambah biaya
+- Mungkin nanti ditinjau apakah anak nggak usah dinaikkan sembari ada surat tembusan ke orang tua supaya orang tua nggak kaget kalau anaknya memang belum bisa menghafal karena tahsinnya masih belum baik
+- Nggak ada jam tambahan karena dari jadwal santri sudah full (seperti jadwal cucian, jadwal tidur, dll). Nah itu kapan kira-kira waktu tambahannya
+Ustadzah Fitri
+- Seperti di kasus Nando, dikomunikasikan ke orang tua dan berhasil tambahan waktu khusus
+Ustadz Wahidi
+- Perlu mengkomunikasikan ke orang tua kalau ini di luar program madrasah
+- Kalau memang setahun tidak ada progres tahsin, harus segera pemanggilan orang tua untuk diajukan private tahsin, dan harus koordinasi dengan kesantrian karena menggangggu jam kesantrian yang ada
+Ustadz Rezky
+- Yang jadi masalah, ketika di ujian lancar, tapi di keseharian, bacaannya tidak lancar
+- Nanti diuji lagi apakah nilai ujian hanya diambil di ujian akhir atau perlu dari nilai keseharian juga (idealnya pakai rata-rata nilai harian)
+- Yang rawan ini dari level tengah ke level siap
+Ustadz Wahidi
+- Kalau nilai sikap menambah nilai tahsin, berarti tidak perlu dimasukkan nilai sikap, jadi lebih fokus ke nilai rata-rata harian
+Ustadz Rezky
+- Kita inginnya ada rapor tahsin (nanti koordinasi sama Waka Kurikulum aja, penulis)
+- Untuk tambahan tahsin, itu pakai jam tahfidz yang ada itu aja. Misalnya 2 halaqah dari 5, untuk bengkel tahsin. Ini harus dipastikan siapa pengajar bengkel tahsinnya
+Ustadz Wahidi
+- Misalnya di jam istirahat siang, ada waktu khusus untuk bengkel tahsin, 2 kali dalam sepekan, dan yang ngajar harus dari internal
+- Nanti akan kita bahas detail di TEKAT (Temu Koordinator Tahfidz dan Tahsin)
 - Aspirasi</t>
-  </si>
-  <si>
-    <t>Tilawah Al-Quran</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>Ust. Akhmad Yudha Nugraha, S.Pd.</t>
-  </si>
-  <si>
-    <t>Doa &amp; Penutup</t>
   </si>
 </sst>
 </file>
@@ -264,10 +292,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,40 +584,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
@@ -613,17 +641,17 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="30">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -710,7 +738,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -725,12 +753,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="60">
+    <row r="19" spans="1:5" ht="409.5">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -778,65 +806,65 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A29:D29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
